--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="141">
   <si>
     <t>_id</t>
   </si>
@@ -216,6 +216,9 @@
     <t>3000,3000,3000,3000,120,800,1</t>
   </si>
   <si>
+    <t>4000,4000,4000,4000,140,1000,2</t>
+  </si>
+  <si>
     <t>15,16,13</t>
   </si>
   <si>
@@ -309,6 +312,9 @@
     <t>3000,3000,3000,60,120,800,1</t>
   </si>
   <si>
+    <t>4000,4000,4000,70,140,1000,2</t>
+  </si>
+  <si>
     <t>7,8,14,18,20</t>
   </si>
   <si>
@@ -396,6 +402,9 @@
     <t>300,100,3000,3000,3000,120,1</t>
   </si>
   <si>
+    <t>360,110,4000,4000,4000,140,2</t>
+  </si>
+  <si>
     <t>10,15,23</t>
   </si>
   <si>
@@ -487,6 +496,9 @@
   </si>
   <si>
     <t>100,3000,6,200,200,800,1</t>
+  </si>
+  <si>
+    <t>110,4000,6,240,240,1000,2</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1491,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -1613,6 +1625,7 @@
         <v>102</v>
       </c>
       <c r="D7" s="2">
+        <f t="shared" ref="D7:D32" si="0">D6+1</f>
         <v>2</v>
       </c>
       <c r="E7" s="2">
@@ -1628,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" ref="I7:I31" si="0">I6*2</f>
+        <f t="shared" ref="I7:I32" si="1">I6*2</f>
         <v>4</v>
       </c>
       <c r="J7" s="2">
@@ -1640,6 +1653,7 @@
         <v>103</v>
       </c>
       <c r="D8" s="2">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E8" s="2">
@@ -1655,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="J8" s="2">
@@ -1667,6 +1681,7 @@
         <v>104</v>
       </c>
       <c r="D9" s="2">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E9" s="2">
@@ -1682,7 +1697,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="J9" s="2">
@@ -1694,6 +1709,7 @@
         <v>105</v>
       </c>
       <c r="D10" s="2">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="E10" s="2">
@@ -1709,7 +1725,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="J10" s="2">
@@ -1721,6 +1737,7 @@
         <v>106</v>
       </c>
       <c r="D11" s="2">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E11" s="2">
@@ -1736,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="J11" s="2">
@@ -1748,6 +1765,7 @@
         <v>107</v>
       </c>
       <c r="D12" s="2">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="E12" s="2">
@@ -1763,7 +1781,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="J12" s="2">
@@ -1775,6 +1793,7 @@
         <v>108</v>
       </c>
       <c r="D13" s="2">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E13" s="2">
@@ -1790,7 +1809,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>256</v>
       </c>
       <c r="J13" s="2">
@@ -1802,6 +1821,7 @@
         <v>109</v>
       </c>
       <c r="D14" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="E14" s="2">
@@ -1817,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>512</v>
       </c>
       <c r="J14" s="2">
@@ -1829,6 +1849,7 @@
         <v>110</v>
       </c>
       <c r="D15" s="2">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E15" s="2">
@@ -1844,7 +1865,7 @@
         <v>4</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1024</v>
       </c>
       <c r="J15" s="2">
@@ -1856,6 +1877,7 @@
         <v>111</v>
       </c>
       <c r="D16" s="2">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E16" s="2">
@@ -1871,7 +1893,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2048</v>
       </c>
       <c r="J16" s="2">
@@ -1883,6 +1905,7 @@
         <v>112</v>
       </c>
       <c r="D17" s="2">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="E17" s="2">
@@ -1898,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4096</v>
       </c>
       <c r="J17" s="2">
@@ -1910,6 +1933,7 @@
         <v>113</v>
       </c>
       <c r="D18" s="2">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="E18" s="2">
@@ -1925,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8192</v>
       </c>
       <c r="J18" s="2">
@@ -1937,6 +1961,7 @@
         <v>114</v>
       </c>
       <c r="D19" s="2">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="E19" s="2">
@@ -1952,7 +1977,7 @@
         <v>5</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16384</v>
       </c>
       <c r="J19" s="2">
@@ -1964,6 +1989,7 @@
         <v>115</v>
       </c>
       <c r="D20" s="2">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="E20" s="2">
@@ -1979,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32768</v>
       </c>
       <c r="J20" s="2">
@@ -1991,6 +2017,7 @@
         <v>116</v>
       </c>
       <c r="D21" s="2">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="E21" s="2">
@@ -2006,7 +2033,7 @@
         <v>5</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65536</v>
       </c>
       <c r="J21" s="2">
@@ -2018,6 +2045,7 @@
         <v>117</v>
       </c>
       <c r="D22" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="E22" s="2">
@@ -2033,7 +2061,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>131072</v>
       </c>
       <c r="J22" s="2">
@@ -2045,6 +2073,7 @@
         <v>118</v>
       </c>
       <c r="D23" s="2">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="E23" s="2">
@@ -2060,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>262144</v>
       </c>
       <c r="J23" s="2">
@@ -2072,6 +2101,7 @@
         <v>119</v>
       </c>
       <c r="D24" s="2">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="E24" s="2">
@@ -2087,7 +2117,7 @@
         <v>5</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>524288</v>
       </c>
       <c r="J24" s="2">
@@ -2099,6 +2129,7 @@
         <v>120</v>
       </c>
       <c r="D25" s="2">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="E25" s="2">
@@ -2114,7 +2145,7 @@
         <v>6</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1048576</v>
       </c>
       <c r="J25" s="2">
@@ -2126,6 +2157,7 @@
         <v>121</v>
       </c>
       <c r="D26" s="2">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="E26" s="2">
@@ -2141,7 +2173,7 @@
         <v>6</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2097152</v>
       </c>
       <c r="J26" s="2">
@@ -2153,6 +2185,7 @@
         <v>122</v>
       </c>
       <c r="D27" s="2">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="E27" s="2">
@@ -2168,7 +2201,7 @@
         <v>6</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4194304</v>
       </c>
       <c r="J27" s="2">
@@ -2180,6 +2213,7 @@
         <v>123</v>
       </c>
       <c r="D28" s="2">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="E28" s="2">
@@ -2195,7 +2229,7 @@
         <v>7</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8388608</v>
       </c>
       <c r="J28" s="2">
@@ -2207,6 +2241,7 @@
         <v>124</v>
       </c>
       <c r="D29" s="2">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="E29" s="2">
@@ -2222,7 +2257,7 @@
         <v>7</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16777216</v>
       </c>
       <c r="J29" s="2">
@@ -2234,6 +2269,7 @@
         <v>125</v>
       </c>
       <c r="D30" s="2">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="E30" s="2">
@@ -2249,7 +2285,7 @@
         <v>7</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33554432</v>
       </c>
       <c r="J30" s="2">
@@ -2261,6 +2297,7 @@
         <v>126</v>
       </c>
       <c r="D31" s="2">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="E31" s="2">
@@ -2276,175 +2313,80 @@
         <v>7</v>
       </c>
       <c r="I31" s="2">
+        <f t="shared" si="1"/>
+        <v>67108864</v>
+      </c>
+      <c r="J31" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="2">
+        <v>127</v>
+      </c>
+      <c r="D32" s="2">
         <f t="shared" si="0"/>
-        <v>67108864</v>
-      </c>
-      <c r="J31" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="7:7">
-      <c r="G32" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="E32" s="2">
+        <v>101</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2">
+        <v>7</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="1"/>
+        <v>134217728</v>
+      </c>
+      <c r="J32" s="2">
+        <v>4007</v>
+      </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="7:7">
       <c r="G33" s="9"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C34" s="2">
-        <v>201</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2">
-        <v>12</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H34" s="2">
-        <v>1</v>
-      </c>
-      <c r="I34" s="2">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C35" s="2">
-        <v>202</v>
-      </c>
-      <c r="D35" s="2">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2">
-        <v>12</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="2">
-        <v>1</v>
-      </c>
-      <c r="I35" s="2">
-        <f t="shared" ref="I35:I59" si="1">I34*2</f>
-        <v>4</v>
-      </c>
-      <c r="J35" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C36" s="2">
-        <v>203</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3</v>
-      </c>
-      <c r="E36" s="2">
-        <v>12</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H36" s="2">
-        <v>1</v>
-      </c>
-      <c r="I36" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="J36" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C37" s="2">
-        <v>204</v>
-      </c>
-      <c r="D37" s="2">
-        <v>4</v>
-      </c>
-      <c r="E37" s="2">
-        <v>12</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H37" s="2">
-        <v>2</v>
-      </c>
-      <c r="I37" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="J37" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C38" s="2">
-        <v>205</v>
-      </c>
-      <c r="D38" s="2">
-        <v>5</v>
-      </c>
-      <c r="E38" s="2">
-        <v>12</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H38" s="2">
-        <v>2</v>
-      </c>
-      <c r="I38" s="2">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="J38" s="2">
-        <v>4007</v>
-      </c>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G38" s="9"/>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C39" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D39" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="H39" s="2">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2">
         <v>2</v>
-      </c>
-      <c r="I39" s="2">
-        <f t="shared" si="1"/>
-        <v>64</v>
       </c>
       <c r="J39" s="2">
         <v>4007</v>
@@ -2452,26 +2394,27 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C40" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D40" s="2">
-        <v>7</v>
+        <f t="shared" ref="D40:D65" si="2">D39+1</f>
+        <v>2</v>
       </c>
       <c r="E40" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="H40" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2">
-        <f t="shared" si="1"/>
-        <v>128</v>
+        <f t="shared" ref="I40:I65" si="3">I39*2</f>
+        <v>4</v>
       </c>
       <c r="J40" s="2">
         <v>4007</v>
@@ -2479,26 +2422,27 @@
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C41" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D41" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E41" s="2">
+        <v>201</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2">
+        <f t="shared" si="3"/>
         <v>8</v>
-      </c>
-      <c r="E41" s="2">
-        <v>12</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H41" s="2">
-        <v>3</v>
-      </c>
-      <c r="I41" s="2">
-        <f t="shared" si="1"/>
-        <v>256</v>
       </c>
       <c r="J41" s="2">
         <v>4007</v>
@@ -2506,26 +2450,27 @@
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C42" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D42" s="2">
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H42" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" s="2">
-        <f t="shared" si="1"/>
-        <v>512</v>
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="J42" s="2">
         <v>4007</v>
@@ -2533,26 +2478,27 @@
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C43" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D43" s="2">
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="E43" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H43" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43" s="2">
-        <f t="shared" si="1"/>
-        <v>1024</v>
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="J43" s="2">
         <v>4007</v>
@@ -2560,26 +2506,27 @@
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C44" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D44" s="2">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="E44" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H44" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" s="2">
-        <f t="shared" si="1"/>
-        <v>2048</v>
+        <f t="shared" si="3"/>
+        <v>64</v>
       </c>
       <c r="J44" s="2">
         <v>4007</v>
@@ -2587,26 +2534,27 @@
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C45" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D45" s="2">
-        <v>12</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="E45" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" s="2">
-        <f t="shared" si="1"/>
-        <v>4096</v>
+        <f t="shared" si="3"/>
+        <v>128</v>
       </c>
       <c r="J45" s="2">
         <v>4007</v>
@@ -2614,26 +2562,27 @@
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C46" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D46" s="2">
-        <v>13</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="E46" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H46" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I46" s="2">
-        <f t="shared" si="1"/>
-        <v>8192</v>
+        <f t="shared" si="3"/>
+        <v>256</v>
       </c>
       <c r="J46" s="2">
         <v>4007</v>
@@ -2641,26 +2590,27 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C47" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D47" s="2">
-        <v>14</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="E47" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H47" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I47" s="2">
-        <f t="shared" si="1"/>
-        <v>16384</v>
+        <f t="shared" si="3"/>
+        <v>512</v>
       </c>
       <c r="J47" s="2">
         <v>4007</v>
@@ -2668,26 +2618,27 @@
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C48" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D48" s="2">
-        <v>15</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="E48" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H48" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" s="2">
-        <f t="shared" si="1"/>
-        <v>32768</v>
+        <f t="shared" si="3"/>
+        <v>1024</v>
       </c>
       <c r="J48" s="2">
         <v>4007</v>
@@ -2695,26 +2646,27 @@
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C49" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D49" s="2">
-        <v>16</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="E49" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I49" s="2">
-        <f t="shared" si="1"/>
-        <v>65536</v>
+        <f t="shared" si="3"/>
+        <v>2048</v>
       </c>
       <c r="J49" s="2">
         <v>4007</v>
@@ -2722,26 +2674,27 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C50" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D50" s="2">
-        <v>17</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="E50" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2">
-        <f t="shared" si="1"/>
-        <v>131072</v>
+        <f t="shared" si="3"/>
+        <v>4096</v>
       </c>
       <c r="J50" s="2">
         <v>4007</v>
@@ -2749,26 +2702,27 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C51" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D51" s="2">
-        <v>18</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="E51" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H51" s="2">
         <v>5</v>
       </c>
       <c r="I51" s="2">
-        <f t="shared" si="1"/>
-        <v>262144</v>
+        <f t="shared" si="3"/>
+        <v>8192</v>
       </c>
       <c r="J51" s="2">
         <v>4007</v>
@@ -2776,26 +2730,27 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C52" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D52" s="2">
-        <v>19</v>
+        <f t="shared" si="2"/>
+        <v>14</v>
       </c>
       <c r="E52" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H52" s="2">
         <v>5</v>
       </c>
       <c r="I52" s="2">
-        <f t="shared" si="1"/>
-        <v>524288</v>
+        <f t="shared" si="3"/>
+        <v>16384</v>
       </c>
       <c r="J52" s="2">
         <v>4007</v>
@@ -2803,26 +2758,27 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C53" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D53" s="2">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>15</v>
       </c>
       <c r="E53" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I53" s="2">
-        <f t="shared" si="1"/>
-        <v>1048576</v>
+        <f t="shared" si="3"/>
+        <v>32768</v>
       </c>
       <c r="J53" s="2">
         <v>4007</v>
@@ -2830,26 +2786,27 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C54" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D54" s="2">
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>16</v>
       </c>
       <c r="E54" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H54" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="1"/>
-        <v>2097152</v>
+        <f t="shared" si="3"/>
+        <v>65536</v>
       </c>
       <c r="J54" s="2">
         <v>4007</v>
@@ -2857,26 +2814,27 @@
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C55" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D55" s="2">
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>17</v>
       </c>
       <c r="E55" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H55" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="1"/>
-        <v>4194304</v>
+        <f t="shared" si="3"/>
+        <v>131072</v>
       </c>
       <c r="J55" s="2">
         <v>4007</v>
@@ -2884,26 +2842,27 @@
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C56" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D56" s="2">
-        <v>23</v>
+        <f t="shared" si="2"/>
+        <v>18</v>
       </c>
       <c r="E56" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H56" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I56" s="2">
-        <f t="shared" si="1"/>
-        <v>8388608</v>
+        <f t="shared" si="3"/>
+        <v>262144</v>
       </c>
       <c r="J56" s="2">
         <v>4007</v>
@@ -2911,26 +2870,27 @@
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C57" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D57" s="2">
-        <v>24</v>
+        <f t="shared" si="2"/>
+        <v>19</v>
       </c>
       <c r="E57" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H57" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I57" s="2">
-        <f t="shared" si="1"/>
-        <v>16777216</v>
+        <f t="shared" si="3"/>
+        <v>524288</v>
       </c>
       <c r="J57" s="2">
         <v>4007</v>
@@ -2938,26 +2898,27 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C58" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D58" s="2">
-        <v>25</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="E58" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H58" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" si="1"/>
-        <v>33554432</v>
+        <f t="shared" si="3"/>
+        <v>1048576</v>
       </c>
       <c r="J58" s="2">
         <v>4007</v>
@@ -2965,55 +2926,83 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C59" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D59" s="2">
-        <v>26</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
       <c r="E59" s="2">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H59" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="1"/>
-        <v>67108864</v>
+        <f t="shared" si="3"/>
+        <v>2097152</v>
       </c>
       <c r="J59" s="2">
         <v>4007</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="7:7">
-      <c r="G60" s="9"/>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C60" s="2">
+        <v>222</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="E60" s="2">
+        <v>201</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" s="2">
+        <v>6</v>
+      </c>
+      <c r="I60" s="2">
+        <f t="shared" si="3"/>
+        <v>4194304</v>
+      </c>
+      <c r="J60" s="2">
+        <v>4007</v>
+      </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C61" s="2">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="D61" s="2">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="E61" s="2">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H61" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I61" s="2">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>8388608</v>
       </c>
       <c r="J61" s="2">
         <v>4007</v>
@@ -3021,26 +3010,27 @@
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C62" s="2">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="D62" s="2">
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="E62" s="2">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H62" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" ref="I62:I86" si="2">I61*2</f>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>16777216</v>
       </c>
       <c r="J62" s="2">
         <v>4007</v>
@@ -3048,26 +3038,27 @@
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C63" s="2">
-        <v>303</v>
+        <v>225</v>
       </c>
       <c r="D63" s="2">
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
       <c r="E63" s="2">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H63" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I63" s="2">
-        <f t="shared" si="2"/>
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>33554432</v>
       </c>
       <c r="J63" s="2">
         <v>4007</v>
@@ -3075,26 +3066,27 @@
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C64" s="2">
-        <v>304</v>
+        <v>226</v>
       </c>
       <c r="D64" s="2">
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>26</v>
       </c>
       <c r="E64" s="2">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F64" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G64" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G64" s="11" t="s">
-        <v>81</v>
-      </c>
       <c r="H64" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I64" s="2">
-        <f t="shared" si="2"/>
-        <v>16</v>
+        <f t="shared" si="3"/>
+        <v>67108864</v>
       </c>
       <c r="J64" s="2">
         <v>4007</v>
@@ -3102,242 +3094,74 @@
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C65" s="2">
-        <v>305</v>
+        <v>227</v>
       </c>
       <c r="D65" s="2">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>27</v>
       </c>
       <c r="E65" s="2">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H65" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I65" s="2">
-        <f t="shared" si="2"/>
-        <v>32</v>
+        <f t="shared" si="3"/>
+        <v>134217728</v>
       </c>
       <c r="J65" s="2">
         <v>4007</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C66" s="2">
-        <v>306</v>
-      </c>
-      <c r="D66" s="2">
-        <v>6</v>
-      </c>
-      <c r="E66" s="2">
-        <v>13</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H66" s="2">
-        <v>2</v>
-      </c>
-      <c r="I66" s="2">
-        <f t="shared" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="J66" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C67" s="2">
-        <v>307</v>
-      </c>
-      <c r="D67" s="2">
-        <v>7</v>
-      </c>
-      <c r="E67" s="2">
-        <v>13</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H67" s="2">
-        <v>3</v>
-      </c>
-      <c r="I67" s="2">
-        <f t="shared" si="2"/>
-        <v>128</v>
-      </c>
-      <c r="J67" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C68" s="2">
-        <v>308</v>
-      </c>
-      <c r="D68" s="2">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2">
-        <v>13</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G68" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H68" s="2">
-        <v>3</v>
-      </c>
-      <c r="I68" s="2">
-        <f t="shared" si="2"/>
-        <v>256</v>
-      </c>
-      <c r="J68" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C69" s="2">
-        <v>309</v>
-      </c>
-      <c r="D69" s="2">
-        <v>9</v>
-      </c>
-      <c r="E69" s="2">
-        <v>13</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H69" s="2">
-        <v>3</v>
-      </c>
-      <c r="I69" s="2">
-        <f t="shared" si="2"/>
-        <v>512</v>
-      </c>
-      <c r="J69" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C70" s="2">
-        <v>310</v>
-      </c>
-      <c r="D70" s="2">
-        <v>10</v>
-      </c>
-      <c r="E70" s="2">
-        <v>13</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H70" s="2">
-        <v>4</v>
-      </c>
-      <c r="I70" s="2">
-        <f t="shared" si="2"/>
-        <v>1024</v>
-      </c>
-      <c r="J70" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C71" s="2">
-        <v>311</v>
-      </c>
-      <c r="D71" s="2">
-        <v>11</v>
-      </c>
-      <c r="E71" s="2">
-        <v>13</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H71" s="2">
-        <v>4</v>
-      </c>
-      <c r="I71" s="2">
-        <f t="shared" si="2"/>
-        <v>2048</v>
-      </c>
-      <c r="J71" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C72" s="2">
-        <v>312</v>
-      </c>
-      <c r="D72" s="2">
-        <v>12</v>
-      </c>
-      <c r="E72" s="2">
-        <v>13</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G72" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="H72" s="2">
-        <v>4</v>
-      </c>
-      <c r="I72" s="2">
-        <f t="shared" si="2"/>
-        <v>4096</v>
-      </c>
-      <c r="J72" s="2">
-        <v>4007</v>
-      </c>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G66" s="9"/>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G67" s="9"/>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G68" s="9"/>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G69" s="9"/>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G70" s="9"/>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G71" s="9"/>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G72" s="9"/>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C73" s="2">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="D73" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E73" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2">
-        <f t="shared" si="2"/>
-        <v>8192</v>
+        <v>2</v>
       </c>
       <c r="J73" s="2">
         <v>4007</v>
@@ -3345,26 +3169,27 @@
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C74" s="2">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D74" s="2">
-        <v>14</v>
+        <f t="shared" ref="D74:D100" si="4">D73+1</f>
+        <v>2</v>
       </c>
       <c r="E74" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H74" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I74" s="2">
-        <f t="shared" si="2"/>
-        <v>16384</v>
+        <f t="shared" ref="I74:I100" si="5">I73*2</f>
+        <v>4</v>
       </c>
       <c r="J74" s="2">
         <v>4007</v>
@@ -3372,26 +3197,27 @@
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C75" s="2">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D75" s="2">
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="E75" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H75" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I75" s="2">
-        <f t="shared" si="2"/>
-        <v>32768</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="J75" s="2">
         <v>4007</v>
@@ -3399,26 +3225,27 @@
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C76" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D76" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="E76" s="2">
+        <v>301</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H76" s="2">
+        <v>2</v>
+      </c>
+      <c r="I76" s="2">
+        <f t="shared" si="5"/>
         <v>16</v>
-      </c>
-      <c r="E76" s="2">
-        <v>13</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G76" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H76" s="2">
-        <v>5</v>
-      </c>
-      <c r="I76" s="2">
-        <f t="shared" si="2"/>
-        <v>65536</v>
       </c>
       <c r="J76" s="2">
         <v>4007</v>
@@ -3426,26 +3253,27 @@
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C77" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D77" s="2">
-        <v>17</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="E77" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H77" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I77" s="2">
-        <f t="shared" si="2"/>
-        <v>131072</v>
+        <f t="shared" si="5"/>
+        <v>32</v>
       </c>
       <c r="J77" s="2">
         <v>4007</v>
@@ -3453,26 +3281,27 @@
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C78" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D78" s="2">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="E78" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H78" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I78" s="2">
-        <f t="shared" si="2"/>
-        <v>262144</v>
+        <f t="shared" si="5"/>
+        <v>64</v>
       </c>
       <c r="J78" s="2">
         <v>4007</v>
@@ -3480,26 +3309,27 @@
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C79" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D79" s="2">
-        <v>19</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H79" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I79" s="2">
-        <f t="shared" si="2"/>
-        <v>524288</v>
+        <f t="shared" si="5"/>
+        <v>128</v>
       </c>
       <c r="J79" s="2">
         <v>4007</v>
@@ -3507,26 +3337,27 @@
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C80" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D80" s="2">
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>8</v>
       </c>
       <c r="E80" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H80" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="2"/>
-        <v>1048576</v>
+        <f t="shared" si="5"/>
+        <v>256</v>
       </c>
       <c r="J80" s="2">
         <v>4007</v>
@@ -3534,26 +3365,27 @@
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C81" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D81" s="2">
-        <v>21</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="E81" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H81" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I81" s="2">
-        <f t="shared" si="2"/>
-        <v>2097152</v>
+        <f t="shared" si="5"/>
+        <v>512</v>
       </c>
       <c r="J81" s="2">
         <v>4007</v>
@@ -3561,26 +3393,27 @@
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C82" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D82" s="2">
-        <v>22</v>
+        <f t="shared" si="4"/>
+        <v>10</v>
       </c>
       <c r="E82" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H82" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I82" s="2">
-        <f t="shared" si="2"/>
-        <v>4194304</v>
+        <f t="shared" si="5"/>
+        <v>1024</v>
       </c>
       <c r="J82" s="2">
         <v>4007</v>
@@ -3588,26 +3421,27 @@
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C83" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D83" s="2">
-        <v>23</v>
+        <f t="shared" si="4"/>
+        <v>11</v>
       </c>
       <c r="E83" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="H83" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I83" s="2">
-        <f t="shared" si="2"/>
-        <v>8388608</v>
+        <f t="shared" si="5"/>
+        <v>2048</v>
       </c>
       <c r="J83" s="2">
         <v>4007</v>
@@ -3615,26 +3449,27 @@
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C84" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D84" s="2">
-        <v>24</v>
+        <f t="shared" si="4"/>
+        <v>12</v>
       </c>
       <c r="E84" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H84" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I84" s="2">
-        <f t="shared" si="2"/>
-        <v>16777216</v>
+        <f t="shared" si="5"/>
+        <v>4096</v>
       </c>
       <c r="J84" s="2">
         <v>4007</v>
@@ -3642,26 +3477,27 @@
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C85" s="2">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D85" s="2">
-        <v>25</v>
+        <f t="shared" si="4"/>
+        <v>13</v>
       </c>
       <c r="E85" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H85" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I85" s="2">
-        <f t="shared" si="2"/>
-        <v>33554432</v>
+        <f t="shared" si="5"/>
+        <v>8192</v>
       </c>
       <c r="J85" s="2">
         <v>4007</v>
@@ -3669,58 +3505,111 @@
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C86" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D86" s="2">
-        <v>26</v>
+        <f t="shared" si="4"/>
+        <v>14</v>
       </c>
       <c r="E86" s="2">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H86" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I86" s="2">
-        <f t="shared" si="2"/>
-        <v>67108864</v>
+        <f t="shared" si="5"/>
+        <v>16384</v>
       </c>
       <c r="J86" s="2">
         <v>4007</v>
       </c>
     </row>
-    <row r="87" s="2" customFormat="1" customHeight="1" spans="7:7">
-      <c r="G87" s="9"/>
-    </row>
-    <row r="88" s="2" customFormat="1" customHeight="1" spans="7:7">
-      <c r="G88" s="9"/>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C87" s="2">
+        <v>315</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="E87" s="2">
+        <v>301</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H87" s="2">
+        <v>5</v>
+      </c>
+      <c r="I87" s="2">
+        <f t="shared" si="5"/>
+        <v>32768</v>
+      </c>
+      <c r="J87" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C88" s="2">
+        <v>316</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="E88" s="2">
+        <v>301</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H88" s="2">
+        <v>5</v>
+      </c>
+      <c r="I88" s="2">
+        <f t="shared" si="5"/>
+        <v>65536</v>
+      </c>
+      <c r="J88" s="2">
+        <v>4007</v>
+      </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C89" s="2">
-        <v>401</v>
+        <v>317</v>
       </c>
       <c r="D89" s="2">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>17</v>
       </c>
       <c r="E89" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>107</v>
+        <v>79</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="H89" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I89" s="2">
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>131072</v>
       </c>
       <c r="J89" s="2">
         <v>4007</v>
@@ -3728,26 +3617,27 @@
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C90" s="2">
-        <v>402</v>
+        <v>318</v>
       </c>
       <c r="D90" s="2">
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>18</v>
       </c>
       <c r="E90" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>108</v>
+        <v>79</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="H90" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I90" s="2">
-        <f t="shared" ref="I90:I114" si="3">I89*2</f>
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>262144</v>
       </c>
       <c r="J90" s="2">
         <v>4007</v>
@@ -3755,26 +3645,27 @@
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C91" s="2">
-        <v>403</v>
+        <v>319</v>
       </c>
       <c r="D91" s="2">
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>19</v>
       </c>
       <c r="E91" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>109</v>
+        <v>79</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="H91" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>524288</v>
       </c>
       <c r="J91" s="2">
         <v>4007</v>
@@ -3782,26 +3673,27 @@
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C92" s="2">
-        <v>404</v>
+        <v>320</v>
       </c>
       <c r="D92" s="2">
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>20</v>
       </c>
       <c r="E92" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>110</v>
+        <v>99</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="H92" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I92" s="2">
-        <f t="shared" si="3"/>
-        <v>16</v>
+        <f t="shared" si="5"/>
+        <v>1048576</v>
       </c>
       <c r="J92" s="2">
         <v>4007</v>
@@ -3809,26 +3701,27 @@
     </row>
     <row r="93" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C93" s="2">
-        <v>405</v>
+        <v>321</v>
       </c>
       <c r="D93" s="2">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>21</v>
       </c>
       <c r="E93" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>111</v>
+        <v>99</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="H93" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I93" s="2">
-        <f t="shared" si="3"/>
-        <v>32</v>
+        <f t="shared" si="5"/>
+        <v>2097152</v>
       </c>
       <c r="J93" s="2">
         <v>4007</v>
@@ -3836,26 +3729,27 @@
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C94" s="2">
-        <v>406</v>
+        <v>322</v>
       </c>
       <c r="D94" s="2">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="E94" s="2">
+        <v>301</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H94" s="2">
         <v>6</v>
       </c>
-      <c r="E94" s="2">
-        <v>14</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="H94" s="2">
-        <v>2</v>
-      </c>
       <c r="I94" s="2">
-        <f t="shared" si="3"/>
-        <v>64</v>
+        <f t="shared" si="5"/>
+        <v>4194304</v>
       </c>
       <c r="J94" s="2">
         <v>4007</v>
@@ -3863,26 +3757,27 @@
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C95" s="2">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="D95" s="2">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="E95" s="2">
+        <v>301</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H95" s="2">
         <v>7</v>
       </c>
-      <c r="E95" s="2">
-        <v>14</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="H95" s="2">
-        <v>3</v>
-      </c>
       <c r="I95" s="2">
-        <f t="shared" si="3"/>
-        <v>128</v>
+        <f t="shared" si="5"/>
+        <v>8388608</v>
       </c>
       <c r="J95" s="2">
         <v>4007</v>
@@ -3890,26 +3785,27 @@
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C96" s="2">
-        <v>408</v>
+        <v>324</v>
       </c>
       <c r="D96" s="2">
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>24</v>
       </c>
       <c r="E96" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>114</v>
+        <v>99</v>
+      </c>
+      <c r="G96" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="H96" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I96" s="2">
-        <f t="shared" si="3"/>
-        <v>256</v>
+        <f t="shared" si="5"/>
+        <v>16777216</v>
       </c>
       <c r="J96" s="2">
         <v>4007</v>
@@ -3917,26 +3813,27 @@
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C97" s="2">
-        <v>409</v>
+        <v>325</v>
       </c>
       <c r="D97" s="2">
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
       <c r="E97" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>115</v>
+        <v>99</v>
+      </c>
+      <c r="G97" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="H97" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I97" s="2">
-        <f t="shared" si="3"/>
-        <v>512</v>
+        <f t="shared" si="5"/>
+        <v>33554432</v>
       </c>
       <c r="J97" s="2">
         <v>4007</v>
@@ -3944,26 +3841,27 @@
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C98" s="2">
-        <v>410</v>
+        <v>326</v>
       </c>
       <c r="D98" s="2">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="E98" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F98" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G98" s="10" t="s">
-        <v>116</v>
+      <c r="G98" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H98" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I98" s="2">
-        <f t="shared" si="3"/>
-        <v>1024</v>
+        <f t="shared" si="5"/>
+        <v>67108864</v>
       </c>
       <c r="J98" s="2">
         <v>4007</v>
@@ -3971,215 +3869,71 @@
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C99" s="2">
-        <v>411</v>
+        <v>327</v>
       </c>
       <c r="D99" s="2">
-        <v>11</v>
+        <f t="shared" si="4"/>
+        <v>27</v>
       </c>
       <c r="E99" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G99" s="10" t="s">
-        <v>117</v>
+      <c r="G99" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="H99" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I99" s="2">
-        <f t="shared" si="3"/>
-        <v>2048</v>
+        <f t="shared" si="5"/>
+        <v>134217728</v>
       </c>
       <c r="J99" s="2">
         <v>4007</v>
       </c>
     </row>
-    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C100" s="2">
-        <v>412</v>
-      </c>
-      <c r="D100" s="2">
-        <v>12</v>
-      </c>
-      <c r="E100" s="2">
-        <v>14</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H100" s="2">
-        <v>4</v>
-      </c>
-      <c r="I100" s="2">
-        <f t="shared" si="3"/>
-        <v>4096</v>
-      </c>
-      <c r="J100" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C101" s="2">
-        <v>413</v>
-      </c>
-      <c r="D101" s="2">
-        <v>13</v>
-      </c>
-      <c r="E101" s="2">
-        <v>14</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="H101" s="2">
-        <v>5</v>
-      </c>
-      <c r="I101" s="2">
-        <f t="shared" si="3"/>
-        <v>8192</v>
-      </c>
-      <c r="J101" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C102" s="2">
-        <v>414</v>
-      </c>
-      <c r="D102" s="2">
-        <v>14</v>
-      </c>
-      <c r="E102" s="2">
-        <v>14</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H102" s="2">
-        <v>5</v>
-      </c>
-      <c r="I102" s="2">
-        <f t="shared" si="3"/>
-        <v>16384</v>
-      </c>
-      <c r="J102" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C103" s="2">
-        <v>415</v>
-      </c>
-      <c r="D103" s="2">
-        <v>15</v>
-      </c>
-      <c r="E103" s="2">
-        <v>14</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="H103" s="2">
-        <v>5</v>
-      </c>
-      <c r="I103" s="2">
-        <f t="shared" si="3"/>
-        <v>32768</v>
-      </c>
-      <c r="J103" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="104" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C104" s="2">
-        <v>416</v>
-      </c>
-      <c r="D104" s="2">
-        <v>16</v>
-      </c>
-      <c r="E104" s="2">
-        <v>14</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H104" s="2">
-        <v>5</v>
-      </c>
-      <c r="I104" s="2">
-        <f t="shared" si="3"/>
-        <v>65536</v>
-      </c>
-      <c r="J104" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="105" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C105" s="2">
-        <v>417</v>
-      </c>
-      <c r="D105" s="2">
-        <v>17</v>
-      </c>
-      <c r="E105" s="2">
-        <v>14</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H105" s="2">
-        <v>5</v>
-      </c>
-      <c r="I105" s="2">
-        <f t="shared" si="3"/>
-        <v>131072</v>
-      </c>
-      <c r="J105" s="2">
-        <v>4007</v>
-      </c>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G100" s="9"/>
+    </row>
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G101" s="9"/>
+    </row>
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G102" s="9"/>
+    </row>
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G103" s="9"/>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G104" s="9"/>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G105" s="9"/>
     </row>
     <row r="106" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C106" s="2">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="D106" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E106" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="H106" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I106" s="2">
-        <f t="shared" si="3"/>
-        <v>262144</v>
+        <v>2</v>
       </c>
       <c r="J106" s="2">
         <v>4007</v>
@@ -4187,26 +3941,27 @@
     </row>
     <row r="107" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C107" s="2">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="D107" s="2">
-        <v>19</v>
+        <f t="shared" ref="D107:D132" si="6">D106+1</f>
+        <v>2</v>
       </c>
       <c r="E107" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H107" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I107" s="2">
-        <f t="shared" si="3"/>
-        <v>524288</v>
+        <f t="shared" ref="I107:I132" si="7">I106*2</f>
+        <v>4</v>
       </c>
       <c r="J107" s="2">
         <v>4007</v>
@@ -4214,26 +3969,27 @@
     </row>
     <row r="108" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C108" s="2">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="D108" s="2">
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="E108" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H108" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I108" s="2">
-        <f t="shared" si="3"/>
-        <v>1048576</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="J108" s="2">
         <v>4007</v>
@@ -4241,26 +3997,27 @@
     </row>
     <row r="109" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C109" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="D109" s="2">
-        <v>21</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="E109" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="H109" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I109" s="2">
-        <f t="shared" si="3"/>
-        <v>2097152</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="J109" s="2">
         <v>4007</v>
@@ -4268,26 +4025,27 @@
     </row>
     <row r="110" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C110" s="2">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="D110" s="2">
-        <v>22</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="E110" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H110" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I110" s="2">
-        <f t="shared" si="3"/>
-        <v>4194304</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="J110" s="2">
         <v>4007</v>
@@ -4295,26 +4053,27 @@
     </row>
     <row r="111" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C111" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="D111" s="2">
-        <v>23</v>
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="E111" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H111" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I111" s="2">
-        <f t="shared" si="3"/>
-        <v>8388608</v>
+        <f t="shared" si="7"/>
+        <v>64</v>
       </c>
       <c r="J111" s="2">
         <v>4007</v>
@@ -4322,26 +4081,27 @@
     </row>
     <row r="112" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C112" s="2">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="D112" s="2">
-        <v>24</v>
+        <f t="shared" si="6"/>
+        <v>7</v>
       </c>
       <c r="E112" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="H112" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I112" s="2">
-        <f t="shared" si="3"/>
-        <v>16777216</v>
+        <f t="shared" si="7"/>
+        <v>128</v>
       </c>
       <c r="J112" s="2">
         <v>4007</v>
@@ -4349,26 +4109,27 @@
     </row>
     <row r="113" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C113" s="2">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="D113" s="2">
-        <v>25</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="E113" s="2">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H113" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I113" s="2">
-        <f t="shared" si="3"/>
-        <v>33554432</v>
+        <f t="shared" si="7"/>
+        <v>256</v>
       </c>
       <c r="J113" s="2">
         <v>4007</v>
@@ -4376,45 +4137,550 @@
     </row>
     <row r="114" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C114" s="2">
+        <v>409</v>
+      </c>
+      <c r="D114" s="2">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="E114" s="2">
+        <v>401</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H114" s="2">
+        <v>3</v>
+      </c>
+      <c r="I114" s="2">
+        <f t="shared" si="7"/>
+        <v>512</v>
+      </c>
+      <c r="J114" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="115" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C115" s="2">
+        <v>410</v>
+      </c>
+      <c r="D115" s="2">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="E115" s="2">
+        <v>401</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H115" s="2">
+        <v>4</v>
+      </c>
+      <c r="I115" s="2">
+        <f t="shared" si="7"/>
+        <v>1024</v>
+      </c>
+      <c r="J115" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C116" s="2">
+        <v>411</v>
+      </c>
+      <c r="D116" s="2">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="E116" s="2">
+        <v>401</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H116" s="2">
+        <v>4</v>
+      </c>
+      <c r="I116" s="2">
+        <f t="shared" si="7"/>
+        <v>2048</v>
+      </c>
+      <c r="J116" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="117" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C117" s="2">
+        <v>412</v>
+      </c>
+      <c r="D117" s="2">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="E117" s="2">
+        <v>401</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H117" s="2">
+        <v>4</v>
+      </c>
+      <c r="I117" s="2">
+        <f t="shared" si="7"/>
+        <v>4096</v>
+      </c>
+      <c r="J117" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="118" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C118" s="2">
+        <v>413</v>
+      </c>
+      <c r="D118" s="2">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="E118" s="2">
+        <v>401</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H118" s="2">
+        <v>5</v>
+      </c>
+      <c r="I118" s="2">
+        <f t="shared" si="7"/>
+        <v>8192</v>
+      </c>
+      <c r="J118" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="119" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C119" s="2">
+        <v>414</v>
+      </c>
+      <c r="D119" s="2">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="E119" s="2">
+        <v>401</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H119" s="2">
+        <v>5</v>
+      </c>
+      <c r="I119" s="2">
+        <f t="shared" si="7"/>
+        <v>16384</v>
+      </c>
+      <c r="J119" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="120" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C120" s="2">
+        <v>415</v>
+      </c>
+      <c r="D120" s="2">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="E120" s="2">
+        <v>401</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H120" s="2">
+        <v>5</v>
+      </c>
+      <c r="I120" s="2">
+        <f t="shared" si="7"/>
+        <v>32768</v>
+      </c>
+      <c r="J120" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="121" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C121" s="2">
+        <v>416</v>
+      </c>
+      <c r="D121" s="2">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="E121" s="2">
+        <v>401</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H121" s="2">
+        <v>5</v>
+      </c>
+      <c r="I121" s="2">
+        <f t="shared" si="7"/>
+        <v>65536</v>
+      </c>
+      <c r="J121" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="122" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C122" s="2">
+        <v>417</v>
+      </c>
+      <c r="D122" s="2">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="E122" s="2">
+        <v>401</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H122" s="2">
+        <v>5</v>
+      </c>
+      <c r="I122" s="2">
+        <f t="shared" si="7"/>
+        <v>131072</v>
+      </c>
+      <c r="J122" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="123" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C123" s="2">
+        <v>418</v>
+      </c>
+      <c r="D123" s="2">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E123" s="2">
+        <v>401</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H123" s="2">
+        <v>5</v>
+      </c>
+      <c r="I123" s="2">
+        <f t="shared" si="7"/>
+        <v>262144</v>
+      </c>
+      <c r="J123" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="124" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C124" s="2">
+        <v>419</v>
+      </c>
+      <c r="D124" s="2">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="E124" s="2">
+        <v>401</v>
+      </c>
+      <c r="F124" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H124" s="2">
+        <v>5</v>
+      </c>
+      <c r="I124" s="2">
+        <f t="shared" si="7"/>
+        <v>524288</v>
+      </c>
+      <c r="J124" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="125" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C125" s="2">
+        <v>420</v>
+      </c>
+      <c r="D125" s="2">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="E125" s="2">
+        <v>401</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H125" s="2">
+        <v>6</v>
+      </c>
+      <c r="I125" s="2">
+        <f t="shared" si="7"/>
+        <v>1048576</v>
+      </c>
+      <c r="J125" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="126" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C126" s="2">
+        <v>421</v>
+      </c>
+      <c r="D126" s="2">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="E126" s="2">
+        <v>401</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H126" s="2">
+        <v>6</v>
+      </c>
+      <c r="I126" s="2">
+        <f t="shared" si="7"/>
+        <v>2097152</v>
+      </c>
+      <c r="J126" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="127" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C127" s="2">
+        <v>422</v>
+      </c>
+      <c r="D127" s="2">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="E127" s="2">
+        <v>401</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H127" s="2">
+        <v>6</v>
+      </c>
+      <c r="I127" s="2">
+        <f t="shared" si="7"/>
+        <v>4194304</v>
+      </c>
+      <c r="J127" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="128" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C128" s="2">
+        <v>423</v>
+      </c>
+      <c r="D128" s="2">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="E128" s="2">
+        <v>401</v>
+      </c>
+      <c r="F128" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H128" s="2">
+        <v>7</v>
+      </c>
+      <c r="I128" s="2">
+        <f t="shared" si="7"/>
+        <v>8388608</v>
+      </c>
+      <c r="J128" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="129" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C129" s="2">
+        <v>424</v>
+      </c>
+      <c r="D129" s="2">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="E129" s="2">
+        <v>401</v>
+      </c>
+      <c r="F129" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H129" s="2">
+        <v>7</v>
+      </c>
+      <c r="I129" s="2">
+        <f t="shared" si="7"/>
+        <v>16777216</v>
+      </c>
+      <c r="J129" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="130" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C130" s="2">
+        <v>425</v>
+      </c>
+      <c r="D130" s="2">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="E130" s="2">
+        <v>401</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H130" s="2">
+        <v>7</v>
+      </c>
+      <c r="I130" s="2">
+        <f t="shared" si="7"/>
+        <v>33554432</v>
+      </c>
+      <c r="J130" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="131" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C131" s="2">
         <v>426</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D131" s="2">
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="E114" s="2">
-        <v>14</v>
-      </c>
-      <c r="F114" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="G114" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H114" s="2">
+      <c r="E131" s="2">
+        <v>401</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H131" s="2">
         <v>7</v>
       </c>
-      <c r="I114" s="2">
-        <f t="shared" si="3"/>
+      <c r="I131" s="2">
+        <f t="shared" si="7"/>
         <v>67108864</v>
       </c>
-      <c r="J114" s="2">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="7:7">
-      <c r="G119" s="9"/>
-    </row>
-    <row r="120" customHeight="1" spans="7:7">
-      <c r="G120" s="9"/>
-    </row>
-    <row r="121" customHeight="1" spans="7:7">
-      <c r="G121" s="9"/>
-    </row>
-    <row r="122" customHeight="1" spans="7:7">
-      <c r="G122" s="9"/>
-    </row>
-    <row r="123" customHeight="1" spans="7:7">
-      <c r="G123" s="9"/>
+      <c r="J131" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="132" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C132" s="2">
+        <v>427</v>
+      </c>
+      <c r="D132" s="2">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="E132" s="2">
+        <v>401</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H132" s="2">
+        <v>7</v>
+      </c>
+      <c r="I132" s="2">
+        <f t="shared" si="7"/>
+        <v>134217728</v>
+      </c>
+      <c r="J132" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="7:7">
+      <c r="G136" s="9"/>
+    </row>
+    <row r="137" customHeight="1" spans="7:7">
+      <c r="G137" s="9"/>
+    </row>
+    <row r="138" customHeight="1" spans="7:7">
+      <c r="G138" s="9"/>
+    </row>
+    <row r="139" customHeight="1" spans="7:7">
+      <c r="G139" s="9"/>
+    </row>
+    <row r="140" customHeight="1" spans="7:7">
+      <c r="G140" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
